--- a/artfynd/A 6253-2026 artfynd.xlsx
+++ b/artfynd/A 6253-2026 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131669967</v>
+        <v>131669949</v>
       </c>
       <c r="B3" t="n">
-        <v>80394</v>
+        <v>80946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419238</v>
+        <v>418551</v>
       </c>
       <c r="R3" t="n">
-        <v>7059296</v>
+        <v>7059452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,19 +874,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>på rot/under rotben på gammal gran i brant med basisk sten</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131669949</v>
+        <v>131669945</v>
       </c>
       <c r="B4" t="n">
-        <v>80946</v>
+        <v>79419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>735</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418551</v>
+        <v>418547</v>
       </c>
       <c r="R4" t="n">
-        <v>7059452</v>
+        <v>7059400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,11 +985,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>på rot/under rotben på gammal gran i brant med basisk sten</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131669945</v>
+        <v>131669967</v>
       </c>
       <c r="B5" t="n">
-        <v>79419</v>
+        <v>80394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418547</v>
+        <v>419238</v>
       </c>
       <c r="R5" t="n">
-        <v>7059400</v>
+        <v>7059296</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,6 +1092,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131669959</v>
+        <v>131669971</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>58057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,34 +1363,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418731</v>
+        <v>418586</v>
       </c>
       <c r="R8" t="n">
-        <v>7059423</v>
+        <v>7059411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131669971</v>
+        <v>131669959</v>
       </c>
       <c r="B9" t="n">
-        <v>58057</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,43 +1479,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418586</v>
+        <v>418731</v>
       </c>
       <c r="R9" t="n">
-        <v>7059411</v>
+        <v>7059423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2140,32 +2140,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131669957</v>
+        <v>131669946</v>
       </c>
       <c r="B15" t="n">
-        <v>79419</v>
+        <v>78272</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418721</v>
+        <v>418539</v>
       </c>
       <c r="R15" t="n">
-        <v>7059412</v>
+        <v>7059417</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,8 +2229,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2247,32 +2263,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131669946</v>
+        <v>131669957</v>
       </c>
       <c r="B16" t="n">
-        <v>78272</v>
+        <v>79419</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418539</v>
+        <v>418721</v>
       </c>
       <c r="R16" t="n">
-        <v>7059417</v>
+        <v>7059412</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,24 +2352,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>barken på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2589,32 +2589,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131669953</v>
+        <v>131669963</v>
       </c>
       <c r="B19" t="n">
-        <v>80331</v>
+        <v>83106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229748</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418620</v>
+        <v>418790</v>
       </c>
       <c r="R19" t="n">
-        <v>7059403</v>
+        <v>7059393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,32 +2696,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131669963</v>
+        <v>131669953</v>
       </c>
       <c r="B20" t="n">
-        <v>83106</v>
+        <v>80331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>229748</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418790</v>
+        <v>418620</v>
       </c>
       <c r="R20" t="n">
-        <v>7059393</v>
+        <v>7059403</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131669955</v>
+        <v>131669973</v>
       </c>
       <c r="B21" t="n">
-        <v>78272</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,34 +2814,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418658</v>
+        <v>418511</v>
       </c>
       <c r="R21" t="n">
-        <v>7059401</v>
+        <v>7059442</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2883,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,24 +2897,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>barken på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2926,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131669973</v>
+        <v>131669955</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>78272</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,39 +2926,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418511</v>
+        <v>418658</v>
       </c>
       <c r="R22" t="n">
-        <v>7059442</v>
+        <v>7059401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3001,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,8 +3004,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 6253-2026 artfynd.xlsx
+++ b/artfynd/A 6253-2026 artfynd.xlsx
@@ -2589,32 +2589,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131669963</v>
+        <v>131669953</v>
       </c>
       <c r="B19" t="n">
-        <v>83106</v>
+        <v>80331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>229748</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418790</v>
+        <v>418620</v>
       </c>
       <c r="R19" t="n">
-        <v>7059393</v>
+        <v>7059403</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,32 +2696,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131669953</v>
+        <v>131669963</v>
       </c>
       <c r="B20" t="n">
-        <v>80331</v>
+        <v>83106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229748</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418620</v>
+        <v>418790</v>
       </c>
       <c r="R20" t="n">
-        <v>7059403</v>
+        <v>7059393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6253-2026 artfynd.xlsx
+++ b/artfynd/A 6253-2026 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131669949</v>
+        <v>131669967</v>
       </c>
       <c r="B3" t="n">
-        <v>80946</v>
+        <v>80394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>735</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418551</v>
+        <v>419238</v>
       </c>
       <c r="R3" t="n">
-        <v>7059452</v>
+        <v>7059296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,9 +874,19 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>på rot/under rotben på gammal gran i brant med basisk sten</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -894,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131669945</v>
+        <v>131669949</v>
       </c>
       <c r="B4" t="n">
-        <v>79419</v>
+        <v>80946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418547</v>
+        <v>418551</v>
       </c>
       <c r="R4" t="n">
-        <v>7059400</v>
+        <v>7059452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,6 +995,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>på rot/under rotben på gammal gran i brant med basisk sten</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,32 +1016,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131669967</v>
+        <v>131669945</v>
       </c>
       <c r="B5" t="n">
-        <v>80394</v>
+        <v>79419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419238</v>
+        <v>418547</v>
       </c>
       <c r="R5" t="n">
-        <v>7059296</v>
+        <v>7059400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,21 +1107,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131669971</v>
+        <v>131669959</v>
       </c>
       <c r="B8" t="n">
-        <v>58057</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,43 +1363,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418586</v>
+        <v>418731</v>
       </c>
       <c r="R8" t="n">
-        <v>7059411</v>
+        <v>7059423</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131669959</v>
+        <v>131669971</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>58057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,34 +1470,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418731</v>
+        <v>418586</v>
       </c>
       <c r="R9" t="n">
-        <v>7059423</v>
+        <v>7059411</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2140,32 +2140,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131669946</v>
+        <v>131669957</v>
       </c>
       <c r="B15" t="n">
-        <v>78272</v>
+        <v>79419</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418539</v>
+        <v>418721</v>
       </c>
       <c r="R15" t="n">
-        <v>7059417</v>
+        <v>7059412</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,24 +2229,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>barken på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2263,32 +2247,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131669957</v>
+        <v>131669946</v>
       </c>
       <c r="B16" t="n">
-        <v>79419</v>
+        <v>78272</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2282,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418721</v>
+        <v>418539</v>
       </c>
       <c r="R16" t="n">
-        <v>7059412</v>
+        <v>7059417</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,8 +2336,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2589,32 +2589,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131669953</v>
+        <v>131669963</v>
       </c>
       <c r="B19" t="n">
-        <v>80331</v>
+        <v>83106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229748</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418620</v>
+        <v>418790</v>
       </c>
       <c r="R19" t="n">
-        <v>7059403</v>
+        <v>7059393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,32 +2696,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131669963</v>
+        <v>131669953</v>
       </c>
       <c r="B20" t="n">
-        <v>83106</v>
+        <v>80331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>229748</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418790</v>
+        <v>418620</v>
       </c>
       <c r="R20" t="n">
-        <v>7059393</v>
+        <v>7059403</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6253-2026 artfynd.xlsx
+++ b/artfynd/A 6253-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131669942</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131669967</v>
+        <v>131669949</v>
       </c>
       <c r="B3" t="n">
-        <v>80394</v>
+        <v>80947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419238</v>
+        <v>418551</v>
       </c>
       <c r="R3" t="n">
-        <v>7059296</v>
+        <v>7059452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,19 +874,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>på rot/under rotben på gammal gran i brant med basisk sten</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131669949</v>
+        <v>131669945</v>
       </c>
       <c r="B4" t="n">
-        <v>80946</v>
+        <v>79420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>735</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418551</v>
+        <v>418547</v>
       </c>
       <c r="R4" t="n">
-        <v>7059452</v>
+        <v>7059400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,11 +985,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>på rot/under rotben på gammal gran i brant med basisk sten</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131669945</v>
+        <v>131669967</v>
       </c>
       <c r="B5" t="n">
-        <v>79419</v>
+        <v>80395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418547</v>
+        <v>419238</v>
       </c>
       <c r="R5" t="n">
-        <v>7059400</v>
+        <v>7059296</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,6 +1092,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1126,7 +1126,7 @@
         <v>131669964</v>
       </c>
       <c r="B6" t="n">
-        <v>78618</v>
+        <v>78619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>131669965</v>
       </c>
       <c r="B7" t="n">
-        <v>83106</v>
+        <v>83107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131669959</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>131669971</v>
       </c>
       <c r="B9" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>131669950</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>131669972</v>
       </c>
       <c r="B11" t="n">
-        <v>78619</v>
+        <v>78620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>131669961</v>
       </c>
       <c r="B12" t="n">
-        <v>79419</v>
+        <v>79420</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>131669962</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>131669947</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131669957</v>
+        <v>131669946</v>
       </c>
       <c r="B15" t="n">
-        <v>79419</v>
+        <v>78273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418721</v>
+        <v>418539</v>
       </c>
       <c r="R15" t="n">
-        <v>7059412</v>
+        <v>7059417</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,8 +2229,24 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2247,32 +2263,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131669946</v>
+        <v>131669957</v>
       </c>
       <c r="B16" t="n">
-        <v>78272</v>
+        <v>79420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418539</v>
+        <v>418721</v>
       </c>
       <c r="R16" t="n">
-        <v>7059417</v>
+        <v>7059412</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,24 +2352,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>barken på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2373,7 +2373,7 @@
         <v>131669968</v>
       </c>
       <c r="B17" t="n">
-        <v>79419</v>
+        <v>79420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>131669954</v>
       </c>
       <c r="B18" t="n">
-        <v>80401</v>
+        <v>80402</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>131669963</v>
       </c>
       <c r="B19" t="n">
-        <v>83106</v>
+        <v>83107</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>131669953</v>
       </c>
       <c r="B20" t="n">
-        <v>80331</v>
+        <v>80332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131669973</v>
+        <v>131669955</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>78273</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,39 +2814,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418511</v>
+        <v>418658</v>
       </c>
       <c r="R21" t="n">
-        <v>7059442</v>
+        <v>7059401</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,7 +2873,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2883,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,8 +2892,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2915,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131669955</v>
+        <v>131669973</v>
       </c>
       <c r="B22" t="n">
-        <v>78272</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,34 +2937,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418658</v>
+        <v>418511</v>
       </c>
       <c r="R22" t="n">
-        <v>7059401</v>
+        <v>7059442</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2985,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,24 +3020,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>barken på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 6253-2026 artfynd.xlsx
+++ b/artfynd/A 6253-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131669942</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131669949</v>
+        <v>131669945</v>
       </c>
       <c r="B3" t="n">
-        <v>80947</v>
+        <v>79423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>735</v>
+        <v>1249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418551</v>
+        <v>418547</v>
       </c>
       <c r="R3" t="n">
-        <v>7059452</v>
+        <v>7059400</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,11 +873,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>på rot/under rotben på gammal gran i brant med basisk sten</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131669945</v>
+        <v>131669949</v>
       </c>
       <c r="B4" t="n">
-        <v>79420</v>
+        <v>80950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418547</v>
+        <v>418551</v>
       </c>
       <c r="R4" t="n">
-        <v>7059400</v>
+        <v>7059452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,6 +980,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>på rot/under rotben på gammal gran i brant med basisk sten</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1004,7 +1004,7 @@
         <v>131669967</v>
       </c>
       <c r="B5" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131669964</v>
       </c>
       <c r="B6" t="n">
-        <v>78619</v>
+        <v>78622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131669965</v>
+        <v>131669971</v>
       </c>
       <c r="B7" t="n">
-        <v>83107</v>
+        <v>58061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,34 +1256,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419019</v>
+        <v>418586</v>
       </c>
       <c r="R7" t="n">
-        <v>7059332</v>
+        <v>7059411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131669959</v>
+        <v>131669965</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>83110</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418731</v>
+        <v>419019</v>
       </c>
       <c r="R8" t="n">
-        <v>7059423</v>
+        <v>7059332</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131669971</v>
+        <v>131669959</v>
       </c>
       <c r="B9" t="n">
-        <v>58058</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,43 +1479,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418586</v>
+        <v>418731</v>
       </c>
       <c r="R9" t="n">
-        <v>7059411</v>
+        <v>7059423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,7 +1578,7 @@
         <v>131669950</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>131669972</v>
       </c>
       <c r="B11" t="n">
-        <v>78620</v>
+        <v>78623</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,45 +1804,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131669961</v>
+        <v>131669962</v>
       </c>
       <c r="B12" t="n">
-        <v>79420</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418747</v>
+        <v>418892</v>
       </c>
       <c r="R12" t="n">
-        <v>7059411</v>
+        <v>7059349</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,50 +1916,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131669962</v>
+        <v>131669961</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>79423</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418892</v>
+        <v>418747</v>
       </c>
       <c r="R13" t="n">
-        <v>7059349</v>
+        <v>7059411</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,7 +2026,7 @@
         <v>131669947</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131669946</v>
+        <v>131669957</v>
       </c>
       <c r="B15" t="n">
-        <v>78273</v>
+        <v>79423</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>1249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418539</v>
+        <v>418721</v>
       </c>
       <c r="R15" t="n">
-        <v>7059417</v>
+        <v>7059412</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,24 +2229,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>barken på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2263,32 +2247,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131669957</v>
+        <v>131669946</v>
       </c>
       <c r="B16" t="n">
-        <v>79420</v>
+        <v>78276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1249</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2282,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418721</v>
+        <v>418539</v>
       </c>
       <c r="R16" t="n">
-        <v>7059412</v>
+        <v>7059417</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,8 +2336,24 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2373,7 +2373,7 @@
         <v>131669968</v>
       </c>
       <c r="B17" t="n">
-        <v>79420</v>
+        <v>79423</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>131669954</v>
       </c>
       <c r="B18" t="n">
-        <v>80402</v>
+        <v>80405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>131669963</v>
       </c>
       <c r="B19" t="n">
-        <v>83107</v>
+        <v>83110</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>131669953</v>
       </c>
       <c r="B20" t="n">
-        <v>80332</v>
+        <v>80335</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131669955</v>
+        <v>131669973</v>
       </c>
       <c r="B21" t="n">
-        <v>78273</v>
+        <v>57902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,34 +2814,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418658</v>
+        <v>418511</v>
       </c>
       <c r="R21" t="n">
-        <v>7059401</v>
+        <v>7059442</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2883,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,24 +2897,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>barken på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2926,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131669973</v>
+        <v>131669955</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>78276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,39 +2926,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418511</v>
+        <v>418658</v>
       </c>
       <c r="R22" t="n">
-        <v>7059442</v>
+        <v>7059401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3001,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,8 +3004,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 6253-2026 artfynd.xlsx
+++ b/artfynd/A 6253-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131669942</v>
+        <v>131669972</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418544</v>
+        <v>418529</v>
       </c>
       <c r="R2" t="n">
-        <v>7059448</v>
+        <v>7059420</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +766,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gren på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,32 +797,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131669967</v>
+        <v>131669949</v>
       </c>
       <c r="B3" t="n">
-        <v>80449</v>
+        <v>81057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419238</v>
+        <v>418551</v>
       </c>
       <c r="R3" t="n">
-        <v>7059296</v>
+        <v>7059452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,19 +889,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>på rot/under rotben på gammal gran i brant med basisk sten</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131669949</v>
+        <v>131669945</v>
       </c>
       <c r="B4" t="n">
-        <v>81001</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>735</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418551</v>
+        <v>418547</v>
       </c>
       <c r="R4" t="n">
-        <v>7059452</v>
+        <v>7059400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,11 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>på rot/under rotben på gammal gran i brant med basisk sten</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131669945</v>
+        <v>131669957</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418547</v>
+        <v>418721</v>
       </c>
       <c r="R5" t="n">
-        <v>7059400</v>
+        <v>7059412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131669964</v>
+        <v>131669961</v>
       </c>
       <c r="B6" t="n">
-        <v>78673</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6443</v>
+        <v>1249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418895</v>
+        <v>418747</v>
       </c>
       <c r="R6" t="n">
-        <v>7059346</v>
+        <v>7059411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,21 +1214,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>gren på gammal död gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1245,54 +1230,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131669971</v>
+        <v>131669968</v>
       </c>
       <c r="B7" t="n">
-        <v>58107</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418586</v>
+        <v>419233</v>
       </c>
       <c r="R7" t="n">
-        <v>7059411</v>
+        <v>7059318</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131669959</v>
+        <v>131669963</v>
       </c>
       <c r="B8" t="n">
-        <v>79315</v>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418731</v>
+        <v>418790</v>
       </c>
       <c r="R8" t="n">
-        <v>7059423</v>
+        <v>7059393</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1447,7 @@
         <v>131669965</v>
       </c>
       <c r="B9" t="n">
-        <v>83161</v>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,32 +1551,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131669950</v>
+        <v>131669970</v>
       </c>
       <c r="B10" t="n">
-        <v>79315</v>
+        <v>92199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1610,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418545</v>
+        <v>418974</v>
       </c>
       <c r="R10" t="n">
-        <v>7059407</v>
+        <v>7059356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131669972</v>
+        <v>131669942</v>
       </c>
       <c r="B11" t="n">
-        <v>78674</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1717,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418529</v>
+        <v>418544</v>
       </c>
       <c r="R11" t="n">
-        <v>7059420</v>
+        <v>7059448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,21 +1749,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>gren på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1804,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131669961</v>
+        <v>131669950</v>
       </c>
       <c r="B12" t="n">
-        <v>79474</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418747</v>
+        <v>418545</v>
       </c>
       <c r="R12" t="n">
-        <v>7059411</v>
+        <v>7059407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,50 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131669962</v>
+        <v>131669959</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418892</v>
+        <v>418731</v>
       </c>
       <c r="R13" t="n">
-        <v>7059349</v>
+        <v>7059423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,50 +1979,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131669947</v>
+        <v>131669964</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6443</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418547</v>
+        <v>418895</v>
       </c>
       <c r="R14" t="n">
-        <v>7059449</v>
+        <v>7059346</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,12 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>hörd ganska nära någonstans västerut</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,6 +2070,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>gren på gammal död gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2140,32 +2101,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131669957</v>
+        <v>131669967</v>
       </c>
       <c r="B15" t="n">
-        <v>79474</v>
+        <v>80493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1249</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418721</v>
+        <v>419238</v>
       </c>
       <c r="R15" t="n">
-        <v>7059412</v>
+        <v>7059296</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,7 +2171,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2181,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,6 +2192,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2247,32 +2223,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131669946</v>
+        <v>131669954</v>
       </c>
       <c r="B16" t="n">
-        <v>78327</v>
+        <v>80500</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418539</v>
+        <v>418585</v>
       </c>
       <c r="R16" t="n">
-        <v>7059417</v>
+        <v>7059409</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,23 +2312,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>barken på gammal gran # Picea abies</t>
+          <t>på basisk lodyta</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2370,45 +2335,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131669968</v>
+        <v>131669947</v>
       </c>
       <c r="B17" t="n">
-        <v>79474</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419233</v>
+        <v>418547</v>
       </c>
       <c r="R17" t="n">
-        <v>7059318</v>
+        <v>7059449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2420,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hörd ganska nära någonstans västerut</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,45 +2452,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131669954</v>
+        <v>131669962</v>
       </c>
       <c r="B18" t="n">
-        <v>80456</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418585</v>
+        <v>418892</v>
       </c>
       <c r="R18" t="n">
-        <v>7059409</v>
+        <v>7059349</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,11 +2548,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>på basisk lodyta</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2589,45 +2564,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131669953</v>
+        <v>131669973</v>
       </c>
       <c r="B19" t="n">
-        <v>80386</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229748</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418620</v>
+        <v>418511</v>
       </c>
       <c r="R19" t="n">
-        <v>7059403</v>
+        <v>7059442</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131669963</v>
+        <v>131669971</v>
       </c>
       <c r="B20" t="n">
-        <v>83161</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,34 +2687,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418790</v>
+        <v>418586</v>
       </c>
       <c r="R20" t="n">
-        <v>7059393</v>
+        <v>7059411</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2766,7 +2755,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2765,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2792,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131669955</v>
+        <v>131669946</v>
       </c>
       <c r="B21" t="n">
-        <v>78327</v>
+        <v>78382</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,10 +2827,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418658</v>
+        <v>418539</v>
       </c>
       <c r="R21" t="n">
-        <v>7059401</v>
+        <v>7059417</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,7 +2862,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2883,7 +2872,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131669973</v>
+        <v>131669955</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>78382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,39 +2926,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gråvalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>418511</v>
+        <v>418658</v>
       </c>
       <c r="R22" t="n">
-        <v>7059442</v>
+        <v>7059401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3001,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,8 +3004,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3035,6 +3035,113 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131669953</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80444</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gråvalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>418620</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7059403</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6253-2026 artfynd.xlsx
+++ b/artfynd/A 6253-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669949</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669945</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669961</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669968</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669963</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669965</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669970</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669942</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669950</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669959</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2098,6 +2163,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669964</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2220,6 +2290,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669967</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2332,6 +2407,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669954</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2449,6 +2529,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669947</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2561,6 +2646,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669962</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2673,6 +2763,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669973</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2789,6 +2884,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669971</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669946</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3035,6 +3140,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669955</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3142,8 +3252,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131669953</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>